--- a/artfynd/A 20828-2024 artfynd.xlsx
+++ b/artfynd/A 20828-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AZ108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629093</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629062</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629063</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629082</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157208</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160550</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629122</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556427</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629072</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1655,6 +1705,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157203</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1756,6 +1811,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157207</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1857,6 +1917,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157209</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157210</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2059,6 +2129,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157214</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2160,6 +2235,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157222</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2261,6 +2341,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157223</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2362,6 +2447,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157211</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2463,6 +2553,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157232</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2560,6 +2655,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629071</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2661,6 +2761,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157206</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2759,6 +2864,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556493</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2856,6 +2966,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629078</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2957,6 +3072,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157217</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3054,6 +3174,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629121</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3159,6 +3284,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157216</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3260,6 +3390,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157219</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3361,6 +3496,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157226</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3462,6 +3602,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157230</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3563,6 +3708,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157231</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3662,6 +3812,11 @@
       <c r="AY31" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157233</t>
         </is>
       </c>
     </row>
@@ -3769,6 +3924,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157240</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3870,6 +4030,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157243</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3971,6 +4136,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160494</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4068,6 +4238,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629081</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4169,6 +4344,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157246</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4270,6 +4450,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160417</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4371,6 +4556,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160531</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4472,6 +4662,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157239</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4573,6 +4768,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157242</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4670,6 +4870,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629115</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4767,6 +4972,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629116</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4864,6 +5074,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629117</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4961,6 +5176,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629119</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5058,6 +5278,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629120</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5159,6 +5384,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157212</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5260,6 +5490,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157213</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5361,6 +5596,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157221</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5458,6 +5698,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629083</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5555,6 +5800,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629095</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5652,6 +5902,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629096</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5749,6 +6004,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629097</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5846,6 +6106,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629098</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5943,6 +6208,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629100</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6040,6 +6310,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629101</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6137,6 +6412,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629103</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6234,6 +6514,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629104</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6331,6 +6616,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629106</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6432,6 +6722,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157220</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6533,6 +6828,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157224</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6634,6 +6934,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157227</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6733,6 +7038,11 @@
       <c r="AY62" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157229</t>
         </is>
       </c>
     </row>
@@ -6840,6 +7150,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157234</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6937,6 +7252,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629076</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7034,6 +7354,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629064</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7131,6 +7456,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629065</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7228,6 +7558,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629066</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7325,6 +7660,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629067</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7422,6 +7762,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629068</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7519,6 +7864,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629070</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7620,6 +7970,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157235</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7721,6 +8076,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157245</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7818,6 +8178,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629080</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7919,6 +8284,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160472</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8017,6 +8387,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556491</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8114,6 +8489,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629090</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8211,6 +8591,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629091</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8308,6 +8693,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629092</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8409,6 +8799,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157202</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8510,6 +8905,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157205</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8611,6 +9011,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157228</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8708,6 +9113,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629084</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8805,6 +9215,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629074</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8907,6 +9322,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629075</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9008,6 +9428,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157215</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9105,6 +9530,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629113</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9206,6 +9636,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157201</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9304,6 +9739,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555883</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9402,6 +9842,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103555960</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9500,6 +9945,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103556450</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9602,6 +10052,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629107</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9699,6 +10154,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629108</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9796,6 +10256,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629109</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9893,6 +10358,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629110</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9990,6 +10460,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629111</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10087,6 +10562,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629112</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10188,6 +10668,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160414</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10289,6 +10774,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160415</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10390,6 +10880,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160416</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10491,6 +10986,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160471</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10592,6 +11092,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105160473</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10689,6 +11194,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629085</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10786,6 +11296,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629086</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10883,6 +11398,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629087</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10984,6 +11504,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157225</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11085,6 +11610,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157218</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11186,6 +11716,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105157244</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11283,8 +11818,122 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103629073</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>